--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122035204</v>
+        <v>122035203</v>
       </c>
       <c r="B8" t="n">
         <v>58019</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670485</v>
+        <v>670490</v>
       </c>
       <c r="R8" t="n">
-        <v>6562583</v>
+        <v>6562614</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122034628</v>
+        <v>122035205</v>
       </c>
       <c r="B9" t="n">
-        <v>57916</v>
+        <v>58079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,25 +1489,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670677</v>
+        <v>670516</v>
       </c>
       <c r="R9" t="n">
-        <v>6562898</v>
+        <v>6562613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122035205</v>
+        <v>122035206</v>
       </c>
       <c r="B10" t="n">
-        <v>58079</v>
+        <v>57744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,25 +1604,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670516</v>
+        <v>670478</v>
       </c>
       <c r="R10" t="n">
-        <v>6562613</v>
+        <v>6562610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122034788</v>
+        <v>122035204</v>
       </c>
       <c r="B11" t="n">
-        <v>57916</v>
+        <v>58019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,20 +1719,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1740,7 +1740,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1752,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670618</v>
+        <v>670485</v>
       </c>
       <c r="R11" t="n">
-        <v>6562832</v>
+        <v>6562583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,12 +1786,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,7 +1811,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1933,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122035206</v>
+        <v>122034788</v>
       </c>
       <c r="B13" t="n">
-        <v>57744</v>
+        <v>57916</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,16 +1953,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1966,14 +1970,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670478</v>
+        <v>670618</v>
       </c>
       <c r="R13" t="n">
-        <v>6562610</v>
+        <v>6562832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122035203</v>
+        <v>122035207</v>
       </c>
       <c r="B14" t="n">
-        <v>58019</v>
+        <v>57525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,20 +2060,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670490</v>
+        <v>670477</v>
       </c>
       <c r="R14" t="n">
-        <v>6562614</v>
+        <v>6562627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122035207</v>
+        <v>122034628</v>
       </c>
       <c r="B15" t="n">
-        <v>57525</v>
+        <v>57916</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,20 +2175,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670477</v>
+        <v>670677</v>
       </c>
       <c r="R15" t="n">
-        <v>6562627</v>
+        <v>6562898</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122035206</v>
+        <v>122035204</v>
       </c>
       <c r="B10" t="n">
-        <v>57744</v>
+        <v>58019</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,20 +1604,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670478</v>
+        <v>670485</v>
       </c>
       <c r="R10" t="n">
-        <v>6562610</v>
+        <v>6562583</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122035204</v>
+        <v>122035206</v>
       </c>
       <c r="B11" t="n">
-        <v>58019</v>
+        <v>57744</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,20 +1719,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670485</v>
+        <v>670478</v>
       </c>
       <c r="R11" t="n">
-        <v>6562583</v>
+        <v>6562610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122035205</v>
+        <v>122035207</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
+        <v>57525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,31 +1493,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670516</v>
+        <v>670477</v>
       </c>
       <c r="R9" t="n">
-        <v>6562613</v>
+        <v>6562627</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122035204</v>
+        <v>122035206</v>
       </c>
       <c r="B10" t="n">
-        <v>58019</v>
+        <v>57744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,20 +1604,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670485</v>
+        <v>670478</v>
       </c>
       <c r="R10" t="n">
-        <v>6562583</v>
+        <v>6562610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122035206</v>
+        <v>122035205</v>
       </c>
       <c r="B11" t="n">
-        <v>57744</v>
+        <v>58079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,25 +1719,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670478</v>
+        <v>670516</v>
       </c>
       <c r="R11" t="n">
-        <v>6562610</v>
+        <v>6562613</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122034788</v>
+        <v>122034628</v>
       </c>
       <c r="B13" t="n">
         <v>57916</v>
@@ -1970,7 +1970,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1982,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670618</v>
+        <v>670677</v>
       </c>
       <c r="R13" t="n">
-        <v>6562832</v>
+        <v>6562898</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,12 +2016,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,7 +2041,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2048,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122035207</v>
+        <v>122035204</v>
       </c>
       <c r="B14" t="n">
-        <v>57525</v>
+        <v>58019</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,20 +2064,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2083,12 +2087,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2097,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670477</v>
+        <v>670485</v>
       </c>
       <c r="R14" t="n">
-        <v>6562627</v>
+        <v>6562583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122034628</v>
+        <v>122034788</v>
       </c>
       <c r="B15" t="n">
         <v>57916</v>
@@ -2196,11 +2200,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670677</v>
+        <v>670618</v>
       </c>
       <c r="R15" t="n">
-        <v>6562898</v>
+        <v>6562832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122035203</v>
+        <v>122034628</v>
       </c>
       <c r="B8" t="n">
-        <v>58019</v>
+        <v>57916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,20 +1374,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670490</v>
+        <v>670677</v>
       </c>
       <c r="R8" t="n">
-        <v>6562614</v>
+        <v>6562898</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122035207</v>
+        <v>122034788</v>
       </c>
       <c r="B9" t="n">
-        <v>57525</v>
+        <v>57916</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,20 +1489,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,14 +1510,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670477</v>
+        <v>670618</v>
       </c>
       <c r="R9" t="n">
-        <v>6562627</v>
+        <v>6562832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,12 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1577,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1707,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122035205</v>
+        <v>122035204</v>
       </c>
       <c r="B11" t="n">
-        <v>58079</v>
+        <v>58019</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,25 +1715,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1756,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670516</v>
+        <v>670485</v>
       </c>
       <c r="R11" t="n">
-        <v>6562613</v>
+        <v>6562583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1937,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122034628</v>
+        <v>122035207</v>
       </c>
       <c r="B13" t="n">
-        <v>57916</v>
+        <v>57525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,20 +1945,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102990</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1972,12 +1968,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1986,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670677</v>
+        <v>670477</v>
       </c>
       <c r="R13" t="n">
-        <v>6562898</v>
+        <v>6562627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,12 +2012,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2037,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2052,7 +2048,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122035204</v>
+        <v>122035203</v>
       </c>
       <c r="B14" t="n">
         <v>58019</v>
@@ -2101,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670485</v>
+        <v>670490</v>
       </c>
       <c r="R14" t="n">
-        <v>6562583</v>
+        <v>6562614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122034788</v>
+        <v>122035205</v>
       </c>
       <c r="B15" t="n">
-        <v>57916</v>
+        <v>58079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,28 +2175,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670618</v>
+        <v>670516</v>
       </c>
       <c r="R15" t="n">
-        <v>6562832</v>
+        <v>6562613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122034628</v>
+        <v>122035205</v>
       </c>
       <c r="B8" t="n">
-        <v>57916</v>
+        <v>58084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670677</v>
+        <v>670516</v>
       </c>
       <c r="R8" t="n">
-        <v>6562898</v>
+        <v>6562613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122034788</v>
+        <v>122034628</v>
       </c>
       <c r="B9" t="n">
-        <v>57916</v>
+        <v>57921</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,7 +1510,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670618</v>
+        <v>670677</v>
       </c>
       <c r="R9" t="n">
-        <v>6562832</v>
+        <v>6562898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1581,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1588,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122035206</v>
+        <v>122035207</v>
       </c>
       <c r="B10" t="n">
-        <v>57744</v>
+        <v>57530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,20 +1604,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1623,12 +1627,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670478</v>
+        <v>670477</v>
       </c>
       <c r="R10" t="n">
-        <v>6562610</v>
+        <v>6562627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122035204</v>
+        <v>122034788</v>
       </c>
       <c r="B11" t="n">
-        <v>58019</v>
+        <v>57921</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,20 +1719,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1736,11 +1740,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670485</v>
+        <v>670618</v>
       </c>
       <c r="R11" t="n">
-        <v>6562583</v>
+        <v>6562832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1821,7 +1821,7 @@
         <v>122034576</v>
       </c>
       <c r="B12" t="n">
-        <v>58052</v>
+        <v>58057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122035207</v>
+        <v>122035206</v>
       </c>
       <c r="B13" t="n">
-        <v>57525</v>
+        <v>57749</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,20 +1945,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670477</v>
+        <v>670478</v>
       </c>
       <c r="R13" t="n">
-        <v>6562627</v>
+        <v>6562610</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122035203</v>
+        <v>122035204</v>
       </c>
       <c r="B14" t="n">
-        <v>58019</v>
+        <v>58024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670490</v>
+        <v>670485</v>
       </c>
       <c r="R14" t="n">
-        <v>6562614</v>
+        <v>6562583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122035205</v>
+        <v>122035203</v>
       </c>
       <c r="B15" t="n">
-        <v>58079</v>
+        <v>58024</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,25 +2175,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670516</v>
+        <v>670490</v>
       </c>
       <c r="R15" t="n">
-        <v>6562613</v>
+        <v>6562614</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122035205</v>
+        <v>122034788</v>
       </c>
       <c r="B8" t="n">
-        <v>58084</v>
+        <v>57921</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,32 +1374,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1411,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670516</v>
+        <v>670618</v>
       </c>
       <c r="R8" t="n">
-        <v>6562613</v>
+        <v>6562832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,12 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1462,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Marie Björklund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1477,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122034628</v>
+        <v>122034576</v>
       </c>
       <c r="B9" t="n">
-        <v>57921</v>
+        <v>58057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,16 +1489,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102990</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,12 +1508,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670677</v>
+        <v>670891</v>
       </c>
       <c r="R9" t="n">
-        <v>6562898</v>
+        <v>6562866</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122035207</v>
+        <v>122034628</v>
       </c>
       <c r="B10" t="n">
-        <v>57530</v>
+        <v>57921</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,20 +1600,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1627,12 +1623,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670477</v>
+        <v>670677</v>
       </c>
       <c r="R10" t="n">
-        <v>6562627</v>
+        <v>6562898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,12 +1667,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,7 +1692,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Edwin Sahlin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1707,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122034788</v>
+        <v>122035204</v>
       </c>
       <c r="B11" t="n">
-        <v>57921</v>
+        <v>58024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,20 +1715,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103042</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1740,7 +1736,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670618</v>
+        <v>670485</v>
       </c>
       <c r="R11" t="n">
-        <v>6562832</v>
+        <v>6562583</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122034576</v>
+        <v>122035203</v>
       </c>
       <c r="B12" t="n">
-        <v>58057</v>
+        <v>58024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,20 +1830,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>670891</v>
+        <v>670490</v>
       </c>
       <c r="R12" t="n">
-        <v>6562866</v>
+        <v>6562614</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122035206</v>
+        <v>122035205</v>
       </c>
       <c r="B13" t="n">
-        <v>57749</v>
+        <v>58084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1945,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>670478</v>
+        <v>670516</v>
       </c>
       <c r="R13" t="n">
-        <v>6562610</v>
+        <v>6562613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122035204</v>
+        <v>122035206</v>
       </c>
       <c r="B14" t="n">
-        <v>58024</v>
+        <v>57749</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,20 +2060,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>670485</v>
+        <v>670478</v>
       </c>
       <c r="R14" t="n">
-        <v>6562583</v>
+        <v>6562610</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122035203</v>
+        <v>122035207</v>
       </c>
       <c r="B15" t="n">
-        <v>58024</v>
+        <v>57530</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,20 +2175,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670490</v>
+        <v>670477</v>
       </c>
       <c r="R15" t="n">
-        <v>6562614</v>
+        <v>6562627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 49418-2023 artfynd.xlsx
+++ b/artfynd/A 49418-2023 artfynd.xlsx
@@ -2413,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126941628</v>
+        <v>126941627</v>
       </c>
       <c r="B17" t="n">
-        <v>56544</v>
+        <v>56539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,26 +2424,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2538,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126941627</v>
+        <v>126941628</v>
       </c>
       <c r="B18" t="n">
-        <v>56539</v>
+        <v>56544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,26 +2549,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
